--- a/docs/assets/Alternate-Timeline-Worksheet.xlsx
+++ b/docs/assets/Alternate-Timeline-Worksheet.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olucdenver-my.sharepoint.com/personal/ernesto_salcedo_cuanschutz_edu/Documents/MHA/Capstone Workshop/Agreement and Scope of work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/github/MHACapstone/docs/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="8_{569B9D2B-C751-2E49-AE9B-C8EEA0A05359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4CB440F-91BC-1740-840D-78EE5BE55DF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F6D78D-7E04-CD44-A28F-B31333B03780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="50880" windowHeight="27980" xr2:uid="{23EC970F-DE6B-9F48-9BEF-E3F42AA93A5B}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="25380" windowHeight="27980" xr2:uid="{23EC970F-DE6B-9F48-9BEF-E3F42AA93A5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Prepare</t>
   </si>
@@ -51,30 +50,6 @@
     <t>Actual</t>
   </si>
   <si>
-    <t>• Outline Capstone Proposal</t>
-  </si>
-  <si>
-    <t>• Submit Capstone Proposal</t>
-  </si>
-  <si>
-    <t>• Complete Data Collection</t>
-  </si>
-  <si>
-    <t>• Practice Presentation</t>
-  </si>
-  <si>
-    <t>• Draft Written Report</t>
-  </si>
-  <si>
-    <t>• Submit Written Report</t>
-  </si>
-  <si>
-    <t>• Submit Digital Resources</t>
-  </si>
-  <si>
-    <t>• Present Capstone</t>
-  </si>
-  <si>
     <t>Should be scheduled before final semester</t>
   </si>
   <si>
@@ -87,15 +62,9 @@
     <t>Plan at least 2 practice sessions</t>
   </si>
   <si>
-    <t>submit a draft to your committee two weeks before you present</t>
-  </si>
-  <si>
     <t>Ideally completed before final semester</t>
   </si>
   <si>
-    <t>• Complete Data Analysis</t>
-  </si>
-  <si>
     <t>Ideally before you submit your written draft</t>
   </si>
   <si>
@@ -108,15 +77,6 @@
     <t>To learn the methods and collect preliminary data</t>
   </si>
   <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>Presentation Day</t>
-  </si>
-  <si>
-    <t>Capstone Proposal</t>
-  </si>
-  <si>
     <t>Number of days</t>
   </si>
   <si>
@@ -156,19 +116,61 @@
     <t>Formulate a hypothesis and specific aims.</t>
   </si>
   <si>
-    <t>• Capstone Start Date</t>
-  </si>
-  <si>
     <t>Number of days between capstone start and your  presentation</t>
   </si>
   <si>
     <t>Must be completed before Starting the Capstone Project</t>
   </si>
   <si>
-    <t>• Capstone Authorization Packet</t>
-  </si>
-  <si>
     <t>Assignment Milestones</t>
+  </si>
+  <si>
+    <t>•  Capstone Authorization Packet</t>
+  </si>
+  <si>
+    <t>•  Capstone Start Date</t>
+  </si>
+  <si>
+    <t>•  Outline Capstone Proposal</t>
+  </si>
+  <si>
+    <t>•  Capstone Proposal - First Draft</t>
+  </si>
+  <si>
+    <t>•  Capstone Proposal - Second Draft</t>
+  </si>
+  <si>
+    <t>•  Submit Capstone Proposal</t>
+  </si>
+  <si>
+    <t>•  Complete Data Collection</t>
+  </si>
+  <si>
+    <t>•  Practice Presentation</t>
+  </si>
+  <si>
+    <t>•  Complete Data Analysis</t>
+  </si>
+  <si>
+    <t>•  Present Capstone</t>
+  </si>
+  <si>
+    <t>•  Submit Written Report</t>
+  </si>
+  <si>
+    <t>•  Submit Digital Resources</t>
+  </si>
+  <si>
+    <t>•   Capstone Report - First Draft</t>
+  </si>
+  <si>
+    <t>•  Capstone Report - Nearly Complete</t>
+  </si>
+  <si>
+    <t>submit a nearly complete draft to your committee two weeks before you present</t>
+  </si>
+  <si>
+    <t>•   Capstone Report - Seond Draft</t>
   </si>
 </sst>
 </file>
@@ -279,7 +281,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,8 +340,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -642,13 +650,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -672,9 +709,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -684,15 +718,15 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -729,15 +763,13 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -750,21 +782,21 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -785,13 +817,13 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,12 +836,32 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -821,6 +873,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCC99"/>
       <color rgb="FFF8EAC1"/>
       <color rgb="FFF9EAC2"/>
     </mruColors>
@@ -1227,380 +1280,335 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4FC70C-6302-9944-8505-32A0259A24ED}">
-  <dimension ref="A3:D30"/>
+  <dimension ref="A3:D34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="12"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="11"/>
     <col min="4" max="4" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:4" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="57"/>
-      <c r="D4" s="49" t="s">
-        <v>32</v>
+      <c r="A4" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="46" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="57"/>
-      <c r="D5" s="49" t="s">
-        <v>32</v>
+      <c r="A5" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="46" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="58"/>
-      <c r="D6" s="49" t="s">
-        <v>32</v>
+      <c r="A6" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="46" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="49"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="56">
-        <v>45658</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>37</v>
+      <c r="A8" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="53">
+        <v>45896</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="56">
-        <v>46002</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>36</v>
+      <c r="A9" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="53">
+        <v>46139</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="52">
+        <f>_xlfn.DAYS(B9,B8)</f>
+        <v>243</v>
+      </c>
+      <c r="D10" s="46" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="55">
-        <f>_xlfn.DAYS(B9,B8)</f>
-        <v>344</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="55"/>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="11"/>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>13</v>
+      <c r="D13" s="27" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="28"/>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="38">
+      <c r="A15" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="35">
         <f>B8-1</f>
-        <v>45657</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="14" t="s">
-        <v>41</v>
+        <v>45895</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="52">
+      <c r="A16" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="49">
         <f>B8</f>
-        <v>45658</v>
-      </c>
-      <c r="C16" s="44">
+        <v>45896</v>
+      </c>
+      <c r="C16" s="41">
         <f>B16</f>
-        <v>45658</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>22</v>
+        <v>45896</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="31"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="24"/>
+      <c r="D17" s="23"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="33">
+        <f>B8+B10*0.05</f>
+        <v>45908.15</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="33">
+        <f>$B$8+$B$10*0.2</f>
+        <v>45944.6</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="33">
+        <f>$B$8+$B$10*0.3</f>
+        <v>45968.9</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="33">
+        <f>B8+B10*0.45</f>
+        <v>46005.35</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="36">
-        <f>B8+B10*0.33</f>
-        <v>45771.519999999997</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="19" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="33">
+        <f>$B$8+$B$10*0.5</f>
+        <v>46017.5</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="24"/>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="34">
+        <f>B26-30</f>
+        <v>46065</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="20"/>
+    </row>
+    <row r="26" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="34">
+        <f>B28-30</f>
+        <v>46095</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="20"/>
+    </row>
+    <row r="27" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="34">
+        <f>B28-15</f>
+        <v>46110</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="34">
+        <f>B29-14</f>
+        <v>46125</v>
+      </c>
+      <c r="C28" s="37"/>
+      <c r="D28" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="51" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="36">
-        <f>B8+B10*0.62</f>
-        <v>45871.28</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="36">
-        <f>B19+14</f>
-        <v>45885.279999999999</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="25"/>
-    </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="21" t="s">
+      <c r="B29" s="50">
+        <f>B9</f>
+        <v>46139</v>
+      </c>
+      <c r="C29" s="39">
+        <f>B29</f>
+        <v>46139</v>
+      </c>
+      <c r="D29" s="36"/>
+    </row>
+    <row r="30" spans="1:4" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="37">
-        <f>B20+30</f>
-        <v>45915.28</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="37">
-        <f>B25-14</f>
-        <v>45988</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
+      <c r="C30" s="38"/>
+      <c r="D30" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="53">
-        <f>B9</f>
-        <v>46002</v>
-      </c>
-      <c r="C25" s="42">
-        <f>B25</f>
-        <v>46002</v>
-      </c>
-      <c r="D25" s="39"/>
-    </row>
-    <row r="26" spans="1:4" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="13"/>
-    </row>
-    <row r="29" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="35"/>
-      <c r="C29" s="13"/>
-    </row>
-    <row r="30" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="35"/>
-      <c r="C30" s="13"/>
+    </row>
+    <row r="32" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="12"/>
+    </row>
+    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+      <c r="C33" s="12"/>
+    </row>
+    <row r="34" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="3"/>
+      <c r="C34" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B549AB-D990-9647-B689-27426ADEB2AB}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="3">
-        <v>45809</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="3">
-        <v>45915</v>
-      </c>
-      <c r="C2">
-        <f>_xlfn.DAYS(B2,B1)</f>
-        <v>106</v>
-      </c>
-      <c r="D2">
-        <f>C2/C4</f>
-        <v>0.32817337461300311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46011</v>
-      </c>
-      <c r="C3">
-        <f>_xlfn.DAYS(B3,B1)</f>
-        <v>202</v>
-      </c>
-      <c r="D3">
-        <f>C3/C4</f>
-        <v>0.62538699690402477</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46132</v>
-      </c>
-      <c r="C4">
-        <f>_xlfn.DAYS(B4,B1)</f>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46002</v>
-      </c>
-      <c r="C7">
-        <f>_xlfn.DAYS(B7,B6)</f>
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="3">
-        <f>B6+(C7*D3)</f>
-        <v>45873.133126934983</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>